--- a/JsonConverter/ExcelFiles/MainDialogueGroup.xlsx
+++ b/JsonConverter/ExcelFiles/MainDialogueGroup.xlsx
@@ -14,30 +14,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_027,dialogue_tutorial_1_1_028,dialogue_tutorial_1_1_029,dialogue_tutorial_1_1_030,dialogue_tutorial_1_1_031,dialogue_tutorial_1_1_032,dialogue_tutorial_1_1_033,dialogue_tutorial_1_1_034,dialogue_tutorial_1_1_035,dialogue_tutorial_1_1_036,dialogue_tutorial_1_1_037,dialogue_tutorial_1_1_038,dialogue_tutorial_1_1_039,dialogue_tutorial_1_1_040,dialogue_tutorial_1_1_041,dialogue_tutorial_1_1_042,dialogue_tutorial_1_1_043</x:t>
+  </x:si>
   <x:si>
     <x:t>DialogueIdList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
   </x:si>
   <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
-    <x:t>튜토리얼 시작</x:t>
+    <x:t>칵테일 제조 성공</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칵테일 제조 실패</x:t>
   </x:si>
   <x:si>
     <x:t>길리안과의 만남</x:t>
-  </x:si>
-  <x:si>
-    <x:t>질의 독백</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
   </x:si>
   <x:si>
     <x:t>string[]</x:t>
@@ -46,25 +40,41 @@
     <x:t>dialogue_group_tutorial_1_3_success</x:t>
   </x:si>
   <x:si>
-    <x:t>Comment</x:t>
+    <x:t>dialogue_group_tutorial_1_3_fail</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">dialogue_tutorial_1_1_009,dialogue_tutorial_1_1_010,dialogue_tutorial_1_1_011,dialogue_tutorial_1_1_012,dialogue_tutorial_1_1_013,dialogue_tutorial_1_1_014,dialogue_tutorial_1_1_015,dialogue_tutorial_1_1_016,dialogue_tutorial_1_1_017,dialogue_tutorial_1_1_018,dialogue_tutorial_1_1_019,dialogue_tutorial_1_1_020,dialogue_tutorial_1_1_021,dialogue_tutorial_1_1_022,dialogue_tutorial_1_1_023,dialogue_tutorial_1_1_024,dialogue_tutorial_1_1_025,dialogue_tutorial_1_1_026
+</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_group_tutorial_1_2</x:t>
   </x:si>
   <x:si>
+    <x:t>dialogue_group_tutorial_1_3</x:t>
+  </x:si>
+  <x:si>
     <x:t>dialogue_group_tutorial_1_1</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_group_tutorial_1_3</x:t>
+    <x:t>질의 독백</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_group_tutorial_1_3_fail</x:t>
+    <x:t>고유 ID</x:t>
   </x:si>
   <x:si>
-    <x:t>칵테일 제조 성공</x:t>
+    <x:t>string</x:t>
   </x:si>
   <x:si>
-    <x:t>칵테일 제조 실패</x:t>
+    <x:t>튜토리얼 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_000,dialogue_tutorial_1_1_001,dialogue_tutorial_1_1_002,dialogue_tutorial_1_1_003,dialogue_tutorial_1_1_004,dialogue_tutorial_1_1_005,dialogue_tutorial_1_1_006,dialogue_tutorial_1_1_007,dialogue_tutorial_1_1_008</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -238,7 +248,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
@@ -277,6 +287,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -947,20 +963,20 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3" ht="15.75" customHeight="1">
@@ -968,10 +984,10 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
@@ -979,9 +995,11 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
-      <x:c r="C4" s="4"/>
+      <x:c r="C4" s="13" t="s">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="D4" s="3"/>
       <x:c r="E4" s="3"/>
       <x:c r="F4" s="3"/>
@@ -997,12 +1015,14 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>13</x:v>
       </x:c>
-      <x:c r="C5" s="5"/>
+      <x:c r="C5" s="14" t="s">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="D5" s="3"/>
       <x:c r="E5" s="3"/>
       <x:c r="F5" s="3"/>
@@ -1018,12 +1038,14 @@
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>16</x:v>
       </x:c>
-      <x:c r="C6" s="5"/>
+      <x:c r="C6" s="5" t="s">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="D6" s="3"/>
       <x:c r="E6" s="3"/>
       <x:c r="F6" s="3"/>
@@ -1039,10 +1061,10 @@
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A7" s="12" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C7" s="4"/>
       <x:c r="D7" s="3"/>
@@ -1060,10 +1082,10 @@
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A8" s="12" t="s">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>15</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C8" s="6"/>
       <x:c r="D8" s="3"/>

--- a/JsonConverter/ExcelFiles/MainDialogueGroup.xlsx
+++ b/JsonConverter/ExcelFiles/MainDialogueGroup.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="24240" windowHeight="13680"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="24240" windowHeight="13395"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Weapon" sheetId="1" r:id="rId4"/>

--- a/JsonConverter/ExcelFiles/MainDialogueGroup.xlsx
+++ b/JsonConverter/ExcelFiles/MainDialogueGroup.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="24240" windowHeight="13395"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="20610" windowHeight="11190"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Weapon" sheetId="1" r:id="rId4"/>
@@ -14,27 +14,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <x:si>
-    <x:t>dialogue_tutorial_1_1_027,dialogue_tutorial_1_1_028,dialogue_tutorial_1_1_029,dialogue_tutorial_1_1_030,dialogue_tutorial_1_1_031,dialogue_tutorial_1_1_032,dialogue_tutorial_1_1_033,dialogue_tutorial_1_1_034,dialogue_tutorial_1_1_035,dialogue_tutorial_1_1_036,dialogue_tutorial_1_1_037,dialogue_tutorial_1_1_038,dialogue_tutorial_1_1_039,dialogue_tutorial_1_1_040,dialogue_tutorial_1_1_041,dialogue_tutorial_1_1_042,dialogue_tutorial_1_1_043</x:t>
+    <x:t>dialogue_tutorial_1_3_000,dialogue_tutorial_1_3_001,dialogue_tutorial_1_3_002,dialogue_tutorial_1_3_003,dialogue_tutorial_1_3_004,dialogue_tutorial_1_3_005,dialogue_tutorial_1_3_006,dialogue_tutorial_1_3_007,dialogue_tutorial_1_3_008,dialogue_tutorial_1_3_009,dialogue_tutorial_1_3_010,dialogue_tutorial_1_3_011</x:t>
   </x:si>
   <x:si>
-    <x:t>DialogueIdList</x:t>
+    <x:t>질의 독백</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
+    <x:t>Comment</x:t>
   </x:si>
   <x:si>
-    <x:t>칵테일 제조 성공</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칵테일 제조 실패</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길리안과의 만남</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
+    <x:t>튜토리얼 시작</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_group_tutorial_1_3_success</x:t>
@@ -43,8 +34,41 @@
     <x:t>dialogue_group_tutorial_1_3_fail</x:t>
   </x:si>
   <x:si>
+    <x:t>dialogue_tutorial_1_1_000,dialogue_tutorial_1_1_001,dialogue_tutorial_1_1_002,dialogue_tutorial_1_1_003,dialogue_tutorial_1_1_004,dialogue_tutorial_1_1_005,dialogue_tutorial_1_1_006,dialogue_tutorial_1_1_007,dialogue_tutorial_1_1_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">dialogue_tutorial_1_1_009,dialogue_tutorial_1_1_010,dialogue_tutorial_1_1_011,dialogue_tutorial_1_1_012,dialogue_tutorial_1_1_013,dialogue_tutorial_1_1_014,dialogue_tutorial_1_1_015,dialogue_tutorial_1_1_016,dialogue_tutorial_1_1_017,dialogue_tutorial_1_1_018,dialogue_tutorial_1_1_019,dialogue_tutorial_1_1_020,dialogue_tutorial_1_1_021,dialogue_tutorial_1_1_022,dialogue_tutorial_1_1_023,dialogue_tutorial_1_1_024,dialogue_tutorial_1_1_025,dialogue_tutorial_1_1_026
 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_000,dialogue_tutorial_1_2_001,dialogue_tutorial_1_2_002,dialogue_tutorial_1_2_003,dialogue_tutorial_1_2_004,dialogue_tutorial_1_2_005,dialogue_tutorial_1_2_006,dialogue_tutorial_1_2_007,dialogue_tutorial_1_2_008,dialogue_tutorial_1_2_009,dialogue_tutorial_1_2_010,dialogue_tutorial_1_2_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_027,dialogue_tutorial_1_1_028,dialogue_tutorial_1_1_029,dialogue_tutorial_1_1_030,dialogue_tutorial_1_1_031,dialogue_tutorial_1_1_032,dialogue_tutorial_1_1_033,dialogue_tutorial_1_1_034,dialogue_tutorial_1_1_035,dialogue_tutorial_1_1_036,dialogue_tutorial_1_1_037,dialogue_tutorial_1_1_038,dialogue_tutorial_1_1_039,dialogue_tutorial_1_1_040,dialogue_tutorial_1_1_041,dialogue_tutorial_1_1_042,dialogue_tutorial_1_1_043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칵테일 제조 실패</x:t>
+  </x:si>
+  <x:si>
+    <x:t>칵테일 제조 성공</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길리안과의 만남</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_group_tutorial_1_2</x:t>
@@ -56,25 +80,7 @@
     <x:t>dialogue_group_tutorial_1_1</x:t>
   </x:si>
   <x:si>
-    <x:t>질의 독백</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>튜토리얼 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_000,dialogue_tutorial_1_1_001,dialogue_tutorial_1_1_002,dialogue_tutorial_1_1_003,dialogue_tutorial_1_1_004,dialogue_tutorial_1_1_005,dialogue_tutorial_1_1_006,dialogue_tutorial_1_1_007,dialogue_tutorial_1_1_008</x:t>
+    <x:t>DialogueIdList</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -963,42 +969,42 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B2" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:3" ht="15.75" customHeight="1">
+      <x:c r="A3" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B3" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C3" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="A4" s="4" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B4" s="4" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
+      <x:c r="C4" s="13" t="s">
         <x:v>6</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A3" s="2" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A4" s="4" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B4" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="13" t="s">
-        <x:v>19</x:v>
       </x:c>
       <x:c r="D4" s="3"/>
       <x:c r="E4" s="3"/>
@@ -1015,13 +1021,13 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C5" s="14" t="s">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D5" s="3"/>
       <x:c r="E5" s="3"/>
@@ -1038,13 +1044,13 @@
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>16</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D6" s="3"/>
       <x:c r="E6" s="3"/>
@@ -1061,12 +1067,14 @@
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A7" s="12" t="s">
-        <x:v>8</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>15</x:v>
       </x:c>
-      <x:c r="C7" s="4"/>
+      <x:c r="C7" s="4" t="s">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="D7" s="3"/>
       <x:c r="E7" s="3"/>
       <x:c r="F7" s="3"/>
@@ -1082,12 +1090,14 @@
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A8" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>16</x:v>
       </x:c>
-      <x:c r="C8" s="6"/>
+      <x:c r="C8" s="6" t="s">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="D8" s="3"/>
       <x:c r="E8" s="3"/>
       <x:c r="F8" s="3"/>

--- a/JsonConverter/ExcelFiles/MainDialogueGroup.xlsx
+++ b/JsonConverter/ExcelFiles/MainDialogueGroup.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="20610" windowHeight="11190"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="17610" windowHeight="9180"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Weapon" sheetId="1" r:id="rId4"/>
@@ -14,61 +14,115 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_000,dialogue_tutorial_1_3_001,dialogue_tutorial_1_3_002,dialogue_tutorial_1_3_003,dialogue_tutorial_1_3_004,dialogue_tutorial_1_3_005,dialogue_tutorial_1_3_006,dialogue_tutorial_1_3_007,dialogue_tutorial_1_3_008,dialogue_tutorial_1_3_009,dialogue_tutorial_1_3_010,dialogue_tutorial_1_3_011</x:t>
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_000,dialogue_tutorial_1_1_001,dialogue_tutorial_1_1_002,dialogue_tutorial_1_1_003,dialogue_tutorial_1_1_004,dialogue_tutorial_1_1_005,dialogue_tutorial_1_1_006,dialogue_tutorial_1_1_007,dialogue_tutorial_1_1_008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_tutorial_1_3_success</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_tutorial_1_3_fail</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_2_000,dialogue_mainDialogue_2_2_001,dialogue_mainDialogue_2_2_002,dialogue_mainDialogue_2_2_003,dialogue_mainDialogue_2_2_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세이 칵테일 제조 실패</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세이 칵테일 제조 성공</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세이와의 만남</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_000,dialogue_tutorial_1_3_001,dialogue_tutorial_1_3_002,dialogue_tutorial_1_3_003,dialogue_tutorial_1_3_004,dialogue_tutorial_1_3_005,dialogue_tutorial_1_3_006,dialogue_tutorial_1_3_007,dialogue_tutorial_1_3_008,dialogue_tutorial_1_3_009,dialogue_tutorial_1_3_010,dialogue_tutorial_1_3_011,dialogue_tutorial_1_3_012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_000,dialogue_mainDialogue_2_1_001,dialogue_mainDialogue_2_1_002,dialogue_mainDialogue_2_1_003,dialogue_mainDialogue_2_1_004,dialogue_mainDialogue_2_1_005,dialogue_mainDialogue_2_1_006,dialogue_mainDialogue_2_1_007,dialogue_mainDialogue_2_1_008,dialogue_mainDialogue_2_1_009,dialogue_mainDialogue_2_1_010,dialogue_mainDialogue_2_1_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainDialogue_1_2_fail</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainDialogue_1_2_success</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainDialogue_1_1_fail</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainDialogue_1_1_success</x:t>
+  </x:si>
+  <x:si>
+    <x:t>튜토리얼 칵테일 제조 성공</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_1_000,dialogue_mainDialogue_1_1_001,dialogue_mainDialogue_1_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도노만 칵테일 제조 실패</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainDialogue_1_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길리안과의 만남</x:t>
   </x:si>
   <x:si>
     <x:t>질의 독백</x:t>
   </x:si>
   <x:si>
+    <x:t>튜토리얼 시작</x:t>
+  </x:si>
+  <x:si>
     <x:t>Comment</x:t>
   </x:si>
   <x:si>
-    <x:t>튜토리얼 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_tutorial_1_3_success</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_tutorial_1_3_fail</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_000,dialogue_tutorial_1_1_001,dialogue_tutorial_1_1_002,dialogue_tutorial_1_1_003,dialogue_tutorial_1_1_004,dialogue_tutorial_1_1_005,dialogue_tutorial_1_1_006,dialogue_tutorial_1_1_007,dialogue_tutorial_1_1_008</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
+    <x:t>dialogue_mainDialogue_1_3_000,dialogue_mainDialogue_1_3_001,dialogue_mainDialogue_1_3_002,dialogue_mainDialogue_1_3_003,dialogue_mainDialogue_1_3_004,dialogue_mainDialogue_1_3_005,dialogue_mainDialogue_1_3_006,dialogue_mainDialogue_1_3_007,dialogue_mainDialogue_1_3_008,dialogue_mainDialogue_1_3_009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도노반과의 만남</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_000,dialogue_mainDialogue_1_2_001,dialogue_mainDialogue_1_2_002,dialogue_mainDialogue_1_2_003,dialogue_mainDialogue_1_2_004,dialogue_mainDialogue_1_2_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_027,dialogue_tutorial_1_1_028,dialogue_tutorial_1_1_029,dialogue_tutorial_1_1_030,dialogue_tutorial_1_1_031,dialogue_tutorial_1_1_032,dialogue_tutorial_1_1_033,dialogue_tutorial_1_1_034,dialogue_tutorial_1_1_035,dialogue_tutorial_1_1_036,dialogue_tutorial_1_1_037,dialogue_tutorial_1_1_038,dialogue_tutorial_1_1_039,dialogue_tutorial_1_1_040,dialogue_tutorial_1_1_041,dialogue_tutorial_1_1_042,dialogue_tutorial_1_1_043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_000,dialogue_tutorial_1_2_001,dialogue_tutorial_1_2_002,dialogue_tutorial_1_2_003,dialogue_tutorial_1_2_004,dialogue_tutorial_1_2_005,dialogue_tutorial_1_2_006,dialogue_tutorial_1_2_007,dialogue_tutorial_1_2_008,dialogue_tutorial_1_2_009,dialogue_tutorial_1_2_010,dialogue_tutorial_1_2_011</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">dialogue_tutorial_1_1_009,dialogue_tutorial_1_1_010,dialogue_tutorial_1_1_011,dialogue_tutorial_1_1_012,dialogue_tutorial_1_1_013,dialogue_tutorial_1_1_014,dialogue_tutorial_1_1_015,dialogue_tutorial_1_1_016,dialogue_tutorial_1_1_017,dialogue_tutorial_1_1_018,dialogue_tutorial_1_1_019,dialogue_tutorial_1_1_020,dialogue_tutorial_1_1_021,dialogue_tutorial_1_1_022,dialogue_tutorial_1_1_023,dialogue_tutorial_1_1_024,dialogue_tutorial_1_1_025,dialogue_tutorial_1_1_026
 </x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_tutorial_1_2_000,dialogue_tutorial_1_2_001,dialogue_tutorial_1_2_002,dialogue_tutorial_1_2_003,dialogue_tutorial_1_2_004,dialogue_tutorial_1_2_005,dialogue_tutorial_1_2_006,dialogue_tutorial_1_2_007,dialogue_tutorial_1_2_008,dialogue_tutorial_1_2_009,dialogue_tutorial_1_2_010,dialogue_tutorial_1_2_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_027,dialogue_tutorial_1_1_028,dialogue_tutorial_1_1_029,dialogue_tutorial_1_1_030,dialogue_tutorial_1_1_031,dialogue_tutorial_1_1_032,dialogue_tutorial_1_1_033,dialogue_tutorial_1_1_034,dialogue_tutorial_1_1_035,dialogue_tutorial_1_1_036,dialogue_tutorial_1_1_037,dialogue_tutorial_1_1_038,dialogue_tutorial_1_1_039,dialogue_tutorial_1_1_040,dialogue_tutorial_1_1_041,dialogue_tutorial_1_1_042,dialogue_tutorial_1_1_043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칵테일 제조 실패</x:t>
-  </x:si>
-  <x:si>
-    <x:t>칵테일 제조 성공</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길리안과의 만남</x:t>
+    <x:t>dialogue_group_mainDialogue_1_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도노반 칵테일 제조 성공</x:t>
+  </x:si>
+  <x:si>
+    <x:t>튜토리얼 칵테일 제조 실패</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DialogueIdList</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_group_tutorial_1_2</x:t>
@@ -80,7 +134,7 @@
     <x:t>dialogue_group_tutorial_1_1</x:t>
   </x:si>
   <x:si>
-    <x:t>DialogueIdList</x:t>
+    <x:t>dialogue_mainDialogue_2_3_000,dialogue_mainDialogue_2_3_001,dialogue_mainDialogue_2_3_002,dialogue_mainDialogue_2_3_003,dialogue_mainDialogue_2_3_004,dialogue_mainDialogue_2_3_005,dialogue_mainDialogue_2_3_006,dialogue_mainDialogue_2_3_007,dialogue_mainDialogue_2_3_008,dialogue_mainDialogue_2_3_009,dialogue_mainDialogue_2_3_010,dialogue_mainDialogue_2_3_011,dialogue_mainDialogue_2_3_012,dialogue_mainDialogue_2_3_013</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -969,42 +1023,42 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C4" s="13" t="s">
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D4" s="3"/>
       <x:c r="E4" s="3"/>
@@ -1021,13 +1075,13 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>1</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C5" s="14" t="s">
-        <x:v>8</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D5" s="3"/>
       <x:c r="E5" s="3"/>
@@ -1044,13 +1098,13 @@
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D6" s="3"/>
       <x:c r="E6" s="3"/>
@@ -1067,13 +1121,13 @@
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A7" s="12" t="s">
-        <x:v>5</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D7" s="3"/>
       <x:c r="E7" s="3"/>
@@ -1090,13 +1144,13 @@
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A8" s="12" t="s">
-        <x:v>4</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>0</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D8" s="3"/>
       <x:c r="E8" s="3"/>
@@ -1112,9 +1166,15 @@
       <x:c r="O8" s="3"/>
     </x:row>
     <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A9" s="6"/>
-      <x:c r="B9" s="6"/>
-      <x:c r="C9" s="6"/>
+      <x:c r="A9" s="12" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="s">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="D9" s="3"/>
       <x:c r="E9" s="3"/>
       <x:c r="F9" s="3"/>
@@ -1129,9 +1189,15 @@
       <x:c r="O9" s="3"/>
     </x:row>
     <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A10" s="7"/>
-      <x:c r="B10" s="7"/>
-      <x:c r="C10" s="7"/>
+      <x:c r="A10" s="12" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B10" s="7" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="C10" s="7" t="s">
+        <x:v>28</x:v>
+      </x:c>
       <x:c r="D10" s="3"/>
       <x:c r="E10" s="3"/>
       <x:c r="F10" s="3"/>
@@ -1146,9 +1212,15 @@
       <x:c r="O10" s="3"/>
     </x:row>
     <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A11" s="7"/>
-      <x:c r="B11" s="7"/>
-      <x:c r="C11" s="7"/>
+      <x:c r="A11" s="12" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B11" s="7" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C11" s="7" t="s">
+        <x:v>26</x:v>
+      </x:c>
       <x:c r="D11" s="3"/>
       <x:c r="E11" s="3"/>
       <x:c r="F11" s="3"/>
@@ -1163,9 +1235,15 @@
       <x:c r="O11" s="3"/>
     </x:row>
     <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A12" s="6"/>
-      <x:c r="B12" s="6"/>
-      <x:c r="C12" s="6"/>
+      <x:c r="A12" s="12" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="s">
+        <x:v>13</x:v>
+      </x:c>
       <x:c r="D12" s="3"/>
       <x:c r="E12" s="3"/>
       <x:c r="F12" s="3"/>
@@ -1180,9 +1258,15 @@
       <x:c r="O12" s="3"/>
     </x:row>
     <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A13" s="4"/>
-      <x:c r="B13" s="4"/>
-      <x:c r="C13" s="4"/>
+      <x:c r="A13" s="12" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B13" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C13" s="4" t="s">
+        <x:v>3</x:v>
+      </x:c>
       <x:c r="D13" s="3"/>
       <x:c r="E13" s="3"/>
       <x:c r="F13" s="3"/>
@@ -1197,9 +1281,15 @@
       <x:c r="O13" s="3"/>
     </x:row>
     <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
-      <x:c r="A14" s="7"/>
-      <x:c r="B14" s="7"/>
-      <x:c r="C14" s="7"/>
+      <x:c r="A14" s="12" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B14" s="7" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C14" s="7" t="s">
+        <x:v>39</x:v>
+      </x:c>
       <x:c r="D14" s="3"/>
       <x:c r="E14" s="3"/>
       <x:c r="F14" s="3"/>

--- a/JsonConverter/ExcelFiles/MainDialogueGroup.xlsx
+++ b/JsonConverter/ExcelFiles/MainDialogueGroup.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="17610" windowHeight="9180"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="22575" windowHeight="13110"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Weapon" sheetId="1" r:id="rId4"/>
@@ -16,113 +16,116 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <x:si>
+    <x:t>dialogue_mainDialogue_2_3_000,dialogue_mainDialogue_2_3_001,dialogue_mainDialogue_2_3_002,dialogue_mainDialogue_2_3_003,dialogue_mainDialogue_2_3_004,dialogue_mainDialogue_2_3_005,dialogue_mainDialogue_2_3_006,dialogue_mainDialogue_2_3_007,dialogue_mainDialogue_2_3_008,dialogue_mainDialogue_2_3_009,dialogue_mainDialogue_2_3_010,dialogue_mainDialogue_2_3_011,dialogue_mainDialogue_2_3_012,dialogue_mainDialogue_2_3_013</x:t>
+  </x:si>
+  <x:si>
     <x:t>dialogue_tutorial_1_1_000,dialogue_tutorial_1_1_001,dialogue_tutorial_1_1_002,dialogue_tutorial_1_1_003,dialogue_tutorial_1_1_004,dialogue_tutorial_1_1_005,dialogue_tutorial_1_1_006,dialogue_tutorial_1_1_007,dialogue_tutorial_1_1_008</x:t>
   </x:si>
   <x:si>
-    <x:t>dialogue_group_tutorial_1_3_success</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_tutorial_1_3_fail</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_2_000,dialogue_mainDialogue_2_2_001,dialogue_mainDialogue_2_2_002,dialogue_mainDialogue_2_2_003,dialogue_mainDialogue_2_2_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세이 칵테일 제조 실패</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세이 칵테일 제조 성공</x:t>
-  </x:si>
-  <x:si>
     <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세이와의 만남</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_000,dialogue_tutorial_1_3_001,dialogue_tutorial_1_3_002,dialogue_tutorial_1_3_003,dialogue_tutorial_1_3_004,dialogue_tutorial_1_3_005,dialogue_tutorial_1_3_006,dialogue_tutorial_1_3_007,dialogue_tutorial_1_3_008,dialogue_tutorial_1_3_009,dialogue_tutorial_1_3_010,dialogue_tutorial_1_3_011,dialogue_tutorial_1_3_012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_1_000,dialogue_mainDialogue_2_1_001,dialogue_mainDialogue_2_1_002,dialogue_mainDialogue_2_1_003,dialogue_mainDialogue_2_1_004,dialogue_mainDialogue_2_1_005,dialogue_mainDialogue_2_1_006,dialogue_mainDialogue_2_1_007,dialogue_mainDialogue_2_1_008,dialogue_mainDialogue_2_1_009,dialogue_mainDialogue_2_1_010,dialogue_mainDialogue_2_1_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainDialogue_1_2_fail</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainDialogue_1_2_success</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainDialogue_1_1_fail</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainDialogue_1_1_success</x:t>
-  </x:si>
-  <x:si>
-    <x:t>튜토리얼 칵테일 제조 성공</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_1_000,dialogue_mainDialogue_1_1_001,dialogue_mainDialogue_1_1_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도노만 칵테일 제조 실패</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainDialogue_1_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길리안과의 만남</x:t>
-  </x:si>
-  <x:si>
-    <x:t>질의 독백</x:t>
-  </x:si>
-  <x:si>
-    <x:t>튜토리얼 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_000,dialogue_mainDialogue_1_3_001,dialogue_mainDialogue_1_3_002,dialogue_mainDialogue_1_3_003,dialogue_mainDialogue_1_3_004,dialogue_mainDialogue_1_3_005,dialogue_mainDialogue_1_3_006,dialogue_mainDialogue_1_3_007,dialogue_mainDialogue_1_3_008,dialogue_mainDialogue_1_3_009</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도노반과의 만남</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_2_000,dialogue_mainDialogue_1_2_001,dialogue_mainDialogue_1_2_002,dialogue_mainDialogue_1_2_003,dialogue_mainDialogue_1_2_004,dialogue_mainDialogue_1_2_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_027,dialogue_tutorial_1_1_028,dialogue_tutorial_1_1_029,dialogue_tutorial_1_1_030,dialogue_tutorial_1_1_031,dialogue_tutorial_1_1_032,dialogue_tutorial_1_1_033,dialogue_tutorial_1_1_034,dialogue_tutorial_1_1_035,dialogue_tutorial_1_1_036,dialogue_tutorial_1_1_037,dialogue_tutorial_1_1_038,dialogue_tutorial_1_1_039,dialogue_tutorial_1_1_040,dialogue_tutorial_1_1_041,dialogue_tutorial_1_1_042,dialogue_tutorial_1_1_043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_000,dialogue_tutorial_1_2_001,dialogue_tutorial_1_2_002,dialogue_tutorial_1_2_003,dialogue_tutorial_1_2_004,dialogue_tutorial_1_2_005,dialogue_tutorial_1_2_006,dialogue_tutorial_1_2_007,dialogue_tutorial_1_2_008,dialogue_tutorial_1_2_009,dialogue_tutorial_1_2_010,dialogue_tutorial_1_2_011</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">dialogue_tutorial_1_1_009,dialogue_tutorial_1_1_010,dialogue_tutorial_1_1_011,dialogue_tutorial_1_1_012,dialogue_tutorial_1_1_013,dialogue_tutorial_1_1_014,dialogue_tutorial_1_1_015,dialogue_tutorial_1_1_016,dialogue_tutorial_1_1_017,dialogue_tutorial_1_1_018,dialogue_tutorial_1_1_019,dialogue_tutorial_1_1_020,dialogue_tutorial_1_1_021,dialogue_tutorial_1_1_022,dialogue_tutorial_1_1_023,dialogue_tutorial_1_1_024,dialogue_tutorial_1_1_025,dialogue_tutorial_1_1_026
 </x:t>
   </x:si>
   <x:si>
+    <x:t>세이와의 만남</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_027,dialogue_tutorial_1_1_028,dialogue_tutorial_1_1_029,dialogue_tutorial_1_1_030,dialogue_tutorial_1_1_031,dialogue_tutorial_1_1_032,dialogue_tutorial_1_1_033,dialogue_tutorial_1_1_034,dialogue_tutorial_1_1_035,dialogue_tutorial_1_1_036,dialogue_tutorial_1_1_037,dialogue_tutorial_1_1_038,dialogue_tutorial_1_1_039,dialogue_tutorial_1_1_040,dialogue_tutorial_1_1_041,dialogue_tutorial_1_1_042,dialogue_tutorial_1_1_043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_tutorial_1_3_fail</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_tutorial_1_3_success</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_000,dialogue_tutorial_1_2_001,dialogue_tutorial_1_2_002,dialogue_tutorial_1_2_003,dialogue_tutorial_1_2_004,dialogue_tutorial_1_2_005,dialogue_tutorial_1_2_006,dialogue_tutorial_1_2_007,dialogue_tutorial_1_2_008,dialogue_tutorial_1_2_009,dialogue_tutorial_1_2_010,dialogue_tutorial_1_2_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_3_000,dialogue_tutorial_1_3_001,dialogue_tutorial_1_3_002,dialogue_tutorial_1_3_003,dialogue_tutorial_1_3_004,dialogue_tutorial_1_3_005,dialogue_tutorial_1_3_006,dialogue_tutorial_1_3_007,dialogue_tutorial_1_3_008,dialogue_tutorial_1_3_009,dialogue_tutorial_1_3_010,dialogue_tutorial_1_3_011,dialogue_tutorial_1_3_012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainDialogue_1_2_fail</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainDialogue_1_1_fail</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainDialogue_1_1_success</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainDialogue_1_2_success</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_1_000,dialogue_mainDialogue_1_1_001,dialogue_mainDialogue_1_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_2_000,dialogue_mainDialogue_2_2_001,dialogue_mainDialogue_2_2_002,dialogue_mainDialogue_2_2_003,dialogue_mainDialogue_2_2_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길리안과의 만남</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도노반과의 만남</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_000,dialogue_mainDialogue_1_2_001,dialogue_mainDialogue_1_2_002,dialogue_mainDialogue_1_2_003,dialogue_mainDialogue_1_2_004,dialogue_mainDialogue_1_2_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>튜토리얼 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>질의 독백</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_1_000,dialogue_mainDialogue_2_1_001,dialogue_mainDialogue_2_1_002,dialogue_mainDialogue_2_1_003,dialogue_mainDialogue_2_1_004,dialogue_mainDialogue_2_1_005,dialogue_mainDialogue_2_1_006,dialogue_mainDialogue_2_1_007,dialogue_mainDialogue_2_1_008,dialogue_mainDialogue_2_1_009,dialogue_mainDialogue_2_1_010,dialogue_mainDialogue_2_1_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>튜토리얼 칵테일 제조 실패</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세이 칵테일 제조 실패</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도노반 칵테일 제조 성공</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도노만 칵테일 제조 실패</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세이 칵테일 제조 성공</x:t>
+  </x:si>
+  <x:si>
+    <x:t>튜토리얼 칵테일 제조 성공</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DialogueIdList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainDialogue_1_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>dialogue_group_mainDialogue_1_2</x:t>
   </x:si>
   <x:si>
-    <x:t>도노반 칵테일 제조 성공</x:t>
-  </x:si>
-  <x:si>
-    <x:t>튜토리얼 칵테일 제조 실패</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DialogueIdList</x:t>
+    <x:t>dialogue_mainDialogue_1_3_000,dialogue_mainDialogue_1_3_001,dialogue_mainDialogue_1_3_002,dialogue_mainDialogue_1_3_003,dialogue_mainDialogue_1_3_004,dialogue_mainDialogue_1_3_005,dialogue_mainDialogue_1_3_006,dialogue_mainDialogue_1_3_007,dialogue_mainDialogue_1_3_008,dialogue_mainDialogue_1_3_009</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_group_tutorial_1_2</x:t>
@@ -132,9 +135,6 @@
   </x:si>
   <x:si>
     <x:t>dialogue_group_tutorial_1_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_3_000,dialogue_mainDialogue_2_3_001,dialogue_mainDialogue_2_3_002,dialogue_mainDialogue_2_3_003,dialogue_mainDialogue_2_3_004,dialogue_mainDialogue_2_3_005,dialogue_mainDialogue_2_3_006,dialogue_mainDialogue_2_3_007,dialogue_mainDialogue_2_3_008,dialogue_mainDialogue_2_3_009,dialogue_mainDialogue_2_3_010,dialogue_mainDialogue_2_3_011,dialogue_mainDialogue_2_3_012,dialogue_mainDialogue_2_3_013</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1023,42 +1023,42 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
         <x:v>25</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="13" t="s">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D4" s="3"/>
       <x:c r="E4" s="3"/>
@@ -1075,13 +1075,13 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C5" s="14" t="s">
-        <x:v>31</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D5" s="3"/>
       <x:c r="E5" s="3"/>
@@ -1098,13 +1098,13 @@
     </x:row>
     <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D6" s="3"/>
       <x:c r="E6" s="3"/>
@@ -1121,13 +1121,13 @@
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A7" s="12" t="s">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D7" s="3"/>
       <x:c r="E7" s="3"/>
@@ -1144,13 +1144,13 @@
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A8" s="12" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D8" s="3"/>
       <x:c r="E8" s="3"/>
@@ -1167,13 +1167,13 @@
     </x:row>
     <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A9" s="12" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B9" s="6" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D9" s="3"/>
       <x:c r="E9" s="3"/>
@@ -1190,13 +1190,13 @@
     </x:row>
     <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A10" s="12" t="s">
-        <x:v>16</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B10" s="7" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>28</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D10" s="3"/>
       <x:c r="E10" s="3"/>
@@ -1213,13 +1213,13 @@
     </x:row>
     <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A11" s="12" t="s">
-        <x:v>17</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B11" s="7" t="s">
-        <x:v>33</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D11" s="3"/>
       <x:c r="E11" s="3"/>
@@ -1236,13 +1236,13 @@
     </x:row>
     <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A12" s="12" t="s">
-        <x:v>32</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>13</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D12" s="3"/>
       <x:c r="E12" s="3"/>
@@ -1259,13 +1259,13 @@
     </x:row>
     <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A13" s="12" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D13" s="3"/>
       <x:c r="E13" s="3"/>
@@ -1282,13 +1282,13 @@
     </x:row>
     <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A14" s="12" t="s">
-        <x:v>15</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="7" t="s">
-        <x:v>5</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C14" s="7" t="s">
-        <x:v>39</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="3"/>
       <x:c r="E14" s="3"/>

--- a/JsonConverter/ExcelFiles/MainDialogueGroup.xlsx
+++ b/JsonConverter/ExcelFiles/MainDialogueGroup.xlsx
@@ -16,125 +16,125 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <x:si>
-    <x:t>dialogue_mainDialogue_2_3_000,dialogue_mainDialogue_2_3_001,dialogue_mainDialogue_2_3_002,dialogue_mainDialogue_2_3_003,dialogue_mainDialogue_2_3_004,dialogue_mainDialogue_2_3_005,dialogue_mainDialogue_2_3_006,dialogue_mainDialogue_2_3_007,dialogue_mainDialogue_2_3_008,dialogue_mainDialogue_2_3_009,dialogue_mainDialogue_2_3_010,dialogue_mainDialogue_2_3_011,dialogue_mainDialogue_2_3_012,dialogue_mainDialogue_2_3_013</x:t>
+    <x:t>dialogue_group_tutorial_1_3_fail</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_tutorial_1_3_success</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_tutorial_1_1_000,dialogue_tutorial_1_1_001,dialogue_tutorial_1_1_002,dialogue_tutorial_1_1_003,dialogue_tutorial_1_1_004,dialogue_tutorial_1_1_005,dialogue_tutorial_1_1_006,dialogue_tutorial_1_1_007,dialogue_tutorial_1_1_008</x:t>
   </x:si>
   <x:si>
+    <x:t>dialogue_tutorial_1_3_000,dialogue_tutorial_1_3_001,dialogue_tutorial_1_3_002,dialogue_tutorial_1_3_003,dialogue_tutorial_1_3_004,dialogue_tutorial_1_3_005,dialogue_tutorial_1_3_006,dialogue_tutorial_1_3_007,dialogue_tutorial_1_3_008,dialogue_tutorial_1_3_009,dialogue_tutorial_1_3_010,dialogue_tutorial_1_3_011,dialogue_tutorial_1_3_012</x:t>
+  </x:si>
+  <x:si>
     <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>길리안과의 만남</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도노반과의 만남</x:t>
+  </x:si>
+  <x:si>
+    <x:t>튜토리얼 칵테일 제조 실패</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세이 칵테일 제조 실패</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도노반 칵테일 제조 성공</x:t>
+  </x:si>
+  <x:si>
+    <x:t>튜토리얼 칵테일 제조 성공</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세이 칵테일 제조 성공</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DialogueIdList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>도노만 칵테일 제조 실패</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_2_000,dialogue_mainDialogue_2_2_001,dialogue_mainDialogue_2_2_002,dialogue_mainDialogue_2_2_003,dialogue_mainDialogue_2_2_004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainDialogue_1_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainDialogue_1_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_1_027,dialogue_tutorial_1_1_028,dialogue_tutorial_1_1_029,dialogue_tutorial_1_1_030,dialogue_tutorial_1_1_031,dialogue_tutorial_1_1_032,dialogue_tutorial_1_1_033,dialogue_tutorial_1_1_034,dialogue_tutorial_1_1_035,dialogue_tutorial_1_1_036,dialogue_tutorial_1_1_037,dialogue_tutorial_1_1_038,dialogue_tutorial_1_1_039,dialogue_tutorial_1_1_040,dialogue_tutorial_1_1_041,dialogue_tutorial_1_1_042,dialogue_tutorial_1_1_043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainDialogue_1_2_success</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainDialogue_1_2_fail</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainDialogue_1_1_fail</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_mainDialogue_1_1_success</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>질의 독백</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세이와의 만남</x:t>
+  </x:si>
+  <x:si>
+    <x:t>튜토리얼 시작</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Comment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_tutorial_1_2_000,dialogue_tutorial_1_2_001,dialogue_tutorial_1_2_002,dialogue_tutorial_1_2_003,dialogue_tutorial_1_2_004,dialogue_tutorial_1_2_005,dialogue_tutorial_1_2_006,dialogue_tutorial_1_2_007,dialogue_tutorial_1_2_008,dialogue_tutorial_1_2_009,dialogue_tutorial_1_2_010,dialogue_tutorial_1_2_011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_2_000,dialogue_mainDialogue_1_2_001,dialogue_mainDialogue_1_2_002,dialogue_mainDialogue_1_2_003,dialogue_mainDialogue_1_2_004,dialogue_mainDialogue_1_2_005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_1_1_000,dialogue_mainDialogue_1_1_001,dialogue_mainDialogue_1_1_002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_mainDialogue_2_3_000,dialogue_mainDialogue_2_3_001,dialogue_mainDialogue_2_3_002,dialogue_mainDialogue_2_3_003,dialogue_mainDialogue_2_3_004,dialogue_mainDialogue_2_3_005,dialogue_mainDialogue_2_3_006,dialogue_mainDialogue_2_3_007,dialogue_mainDialogue_2_3_008,dialogue_mainDialogue_2_3_009,dialogue_mainDialogue_2_3_010,dialogue_mainDialogue_2_3_011,dialogue_mainDialogue_2_3_012,dialogue_mainDialogue_2_3_013,dialogue_mainDialogue_2_3_014,dialogue_mainDialogue_2_3_015,dialogue_mainDialogue_2_3_016,dialogue_mainDialogue_2_3_017,dialogue_mainDialogue_2_3_018,dialogue_mainDialogue_2_3_019,dialogue_mainDialogue_2_3_020,dialogue_mainDialogue_2_3_021,dialogue_mainDialogue_2_3_022,dialogue_mainDialogue_2_3_023,dialogue_mainDialogue_2_3_024,dialogue_mainDialogue_2_3_025</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">dialogue_tutorial_1_1_009,dialogue_tutorial_1_1_010,dialogue_tutorial_1_1_011,dialogue_tutorial_1_1_012,dialogue_tutorial_1_1_013,dialogue_tutorial_1_1_014,dialogue_tutorial_1_1_015,dialogue_tutorial_1_1_016,dialogue_tutorial_1_1_017,dialogue_tutorial_1_1_018,dialogue_tutorial_1_1_019,dialogue_tutorial_1_1_020,dialogue_tutorial_1_1_021,dialogue_tutorial_1_1_022,dialogue_tutorial_1_1_023,dialogue_tutorial_1_1_024,dialogue_tutorial_1_1_025,dialogue_tutorial_1_1_026
 </x:t>
   </x:si>
   <x:si>
-    <x:t>세이와의 만남</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_1_027,dialogue_tutorial_1_1_028,dialogue_tutorial_1_1_029,dialogue_tutorial_1_1_030,dialogue_tutorial_1_1_031,dialogue_tutorial_1_1_032,dialogue_tutorial_1_1_033,dialogue_tutorial_1_1_034,dialogue_tutorial_1_1_035,dialogue_tutorial_1_1_036,dialogue_tutorial_1_1_037,dialogue_tutorial_1_1_038,dialogue_tutorial_1_1_039,dialogue_tutorial_1_1_040,dialogue_tutorial_1_1_041,dialogue_tutorial_1_1_042,dialogue_tutorial_1_1_043</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_tutorial_1_3_fail</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_tutorial_1_3_success</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_2_000,dialogue_tutorial_1_2_001,dialogue_tutorial_1_2_002,dialogue_tutorial_1_2_003,dialogue_tutorial_1_2_004,dialogue_tutorial_1_2_005,dialogue_tutorial_1_2_006,dialogue_tutorial_1_2_007,dialogue_tutorial_1_2_008,dialogue_tutorial_1_2_009,dialogue_tutorial_1_2_010,dialogue_tutorial_1_2_011</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_tutorial_1_3_000,dialogue_tutorial_1_3_001,dialogue_tutorial_1_3_002,dialogue_tutorial_1_3_003,dialogue_tutorial_1_3_004,dialogue_tutorial_1_3_005,dialogue_tutorial_1_3_006,dialogue_tutorial_1_3_007,dialogue_tutorial_1_3_008,dialogue_tutorial_1_3_009,dialogue_tutorial_1_3_010,dialogue_tutorial_1_3_011,dialogue_tutorial_1_3_012</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainDialogue_1_2_fail</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainDialogue_1_1_fail</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainDialogue_1_1_success</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainDialogue_1_2_success</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_1_000,dialogue_mainDialogue_1_1_001,dialogue_mainDialogue_1_1_002</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_2_2_000,dialogue_mainDialogue_2_2_001,dialogue_mainDialogue_2_2_002,dialogue_mainDialogue_2_2_003,dialogue_mainDialogue_2_2_004</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>길리안과의 만남</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도노반과의 만남</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_2_000,dialogue_mainDialogue_1_2_001,dialogue_mainDialogue_1_2_002,dialogue_mainDialogue_1_2_003,dialogue_mainDialogue_1_2_004,dialogue_mainDialogue_1_2_005</x:t>
-  </x:si>
-  <x:si>
-    <x:t>튜토리얼 시작</x:t>
-  </x:si>
-  <x:si>
-    <x:t>질의 독백</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Comment</x:t>
+    <x:t>dialogue_mainDialogue_1_3_000,dialogue_mainDialogue_1_3_001,dialogue_mainDialogue_1_3_002,dialogue_mainDialogue_1_3_003,dialogue_mainDialogue_1_3_004,dialogue_mainDialogue_1_3_005,dialogue_mainDialogue_1_3_006,dialogue_mainDialogue_1_3_007,dialogue_mainDialogue_1_3_008,dialogue_mainDialogue_1_3_009</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_mainDialogue_2_1_000,dialogue_mainDialogue_2_1_001,dialogue_mainDialogue_2_1_002,dialogue_mainDialogue_2_1_003,dialogue_mainDialogue_2_1_004,dialogue_mainDialogue_2_1_005,dialogue_mainDialogue_2_1_006,dialogue_mainDialogue_2_1_007,dialogue_mainDialogue_2_1_008,dialogue_mainDialogue_2_1_009,dialogue_mainDialogue_2_1_010,dialogue_mainDialogue_2_1_011</x:t>
   </x:si>
   <x:si>
-    <x:t>튜토리얼 칵테일 제조 실패</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세이 칵테일 제조 실패</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도노반 칵테일 제조 성공</x:t>
-  </x:si>
-  <x:si>
-    <x:t>도노만 칵테일 제조 실패</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세이 칵테일 제조 성공</x:t>
-  </x:si>
-  <x:si>
-    <x:t>튜토리얼 칵테일 제조 성공</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DialogueIdList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainDialogue_1_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_mainDialogue_1_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_mainDialogue_1_3_000,dialogue_mainDialogue_1_3_001,dialogue_mainDialogue_1_3_002,dialogue_mainDialogue_1_3_003,dialogue_mainDialogue_1_3_004,dialogue_mainDialogue_1_3_005,dialogue_mainDialogue_1_3_006,dialogue_mainDialogue_1_3_007,dialogue_mainDialogue_1_3_008,dialogue_mainDialogue_1_3_009</x:t>
+    <x:t>dialogue_group_tutorial_1_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>dialogue_group_tutorial_1_3</x:t>
   </x:si>
   <x:si>
     <x:t>dialogue_group_tutorial_1_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_tutorial_1_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>dialogue_group_tutorial_1_1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1023,42 +1023,42 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1"/>
     </x:row>
     <x:row r="2" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A2" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A3" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B3" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C3" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C4" s="13" t="s">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D4" s="3"/>
       <x:c r="E4" s="3"/>
@@ -1075,13 +1075,13 @@
     </x:row>
     <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C5" s="14" t="s">
-        <x:v>3</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D5" s="3"/>
       <x:c r="E5" s="3"/>
@@ -1101,10 +1101,10 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>5</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D6" s="3"/>
       <x:c r="E6" s="3"/>
@@ -1121,13 +1121,13 @@
     </x:row>
     <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A7" s="12" t="s">
-        <x:v>6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D7" s="3"/>
       <x:c r="E7" s="3"/>
@@ -1144,13 +1144,13 @@
     </x:row>
     <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A8" s="12" t="s">
-        <x:v>7</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>32</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>9</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D8" s="3"/>
       <x:c r="E8" s="3"/>
@@ -1167,13 +1167,13 @@
     </x:row>
     <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A9" s="12" t="s">
-        <x:v>34</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>14</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D9" s="3"/>
       <x:c r="E9" s="3"/>
@@ -1190,13 +1190,13 @@
     </x:row>
     <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A10" s="12" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B10" s="7" t="s">
-        <x:v>30</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C10" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D10" s="3"/>
       <x:c r="E10" s="3"/>
@@ -1213,13 +1213,13 @@
     </x:row>
     <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A11" s="12" t="s">
-        <x:v>12</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B11" s="7" t="s">
-        <x:v>29</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C11" s="7" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D11" s="3"/>
       <x:c r="E11" s="3"/>
@@ -1236,13 +1236,13 @@
     </x:row>
     <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A12" s="12" t="s">
-        <x:v>35</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>26</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D12" s="3"/>
       <x:c r="E12" s="3"/>
@@ -1259,13 +1259,13 @@
     </x:row>
     <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A13" s="12" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D13" s="3"/>
       <x:c r="E13" s="3"/>
@@ -1282,13 +1282,13 @@
     </x:row>
     <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
       <x:c r="A14" s="12" t="s">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B14" s="7" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="7" t="s">
-        <x:v>0</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D14" s="3"/>
       <x:c r="E14" s="3"/>
